--- a/output/pdf_financials_xlsx/ATHR.xlsx
+++ b/output/pdf_financials_xlsx/ATHR.xlsx
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.017238</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.011602</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.022481</v>
       </c>
     </row>
     <row r="35">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.017238</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.011602</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.022481</v>
       </c>
     </row>
     <row r="37">
@@ -1344,13 +1344,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.024786</v>
+        <v>0.007548</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.01915</v>
+        <v>0.007548</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.29043</v>
+        <v>0.267949</v>
       </c>
     </row>
     <row r="49">
@@ -2557,13 +2557,13 @@
         </is>
       </c>
       <c r="B124" s="3" t="n">
-        <v>0</v>
+        <v>-0.048255</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.046644</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.046322</v>
       </c>
     </row>
     <row r="125">
@@ -2573,13 +2573,13 @@
         </is>
       </c>
       <c r="B125" s="3" t="n">
-        <v>0</v>
+        <v>-0.048255</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.046644</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.046322</v>
       </c>
     </row>
     <row r="126">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -5189,7 +5189,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E80" s="5" t="n">
         <v>-0.048255</v>
       </c>

--- a/output/pdf_financials_xlsx/ATHR.xlsx
+++ b/output/pdf_financials_xlsx/ATHR.xlsx
@@ -1654,13 +1654,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.0375</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.07818600000000001</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.055586</v>
       </c>
     </row>
     <row r="68">
@@ -5280,7 +5280,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E83" s="5" t="n">
         <v>0.22</v>
       </c>
